--- a/scenarios/live/deliverables/요구사항_추적표.xlsx
+++ b/scenarios/live/deliverables/요구사항_추적표.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,56 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/7ad54eaba34b39daf406f6fe3449494cc3705018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260730-co-wbs-pause-pp-routing-md-cleanup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:14:57.925+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Abraxaspark91(pusher)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>github(demo, meetings/2026-07-30-steering.md)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>진행을 승인하되, CO 임시 운영 통제·교차 모듈 영향도·마스터데이터 이관 및 복구 기준·테스트 게이트·컴플라이언스 책임자를 확정한 후 착수한다. PP 라우팅 표준화는 자재/BOM 정비와 승인 완료를 전제로 8월 목표 착수로만 관리한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CO 내부오더 WBS 전환 보류와 임시 운영·영향도·재검토 조건, PP 라우팅 표준화의 조건부 8월 착수, 자재/BOM 정비·이관·복구 기준 및 교차 모듈 테스트 게이트를 반영한다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>릴리즈 범위 정의서; CO 내부오더 임시 운영 및 영향도 계획서; PP 라우팅 표준화 계획서; 마스터데이터 정비 및 이관 계획서; 테스트 시나리오 및 회귀 테스트 계획서; 변경관리·감사추적·고객공지 계획서</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/52f4790dff50ef34a5c6c4126eea351f2c32e3c4</t>
         </is>
       </c>
     </row>

--- a/scenarios/live/deliverables/요구사항_추적표.xlsx
+++ b/scenarios/live/deliverables/요구사항_추적표.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,56 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/52f4790dff50ef34a5c6c4126eea351f2c32e3c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20260725-SD-FI-KNA1-승인실행</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01T14:16:46.511+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>홍길동(고객사) &lt;abraxaspark91@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>outlook(demo, 첨부파일 파싱됨)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>영향분석·필드 및 재처리 규칙·개인정보 검토·직무분리·승인 증적과 객관적 테스트 합격 기준을 산출물에 반영했으며, 최종 승인 기준과 세부 설계 확정 전에는 개발·테스트·배포를 확정하지 않고 승인 게이트 통과 범위만 다음 릴리즈에 반영한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>통합테스트 3차 SD-FI 5건 및 W-102 KNA1 매핑 변경을 다음 릴리즈 대상으로 반영하되, 승인 기준·영향분석·컴플라이언스 확인 전까지 개발·테스트는 승인 게이트 대기 상태입니다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>통합테스트 시나리오; WRICEF W-102 인터페이스 매핑 정의서; 고객 마스터 필드 정의서; 인터페이스 운영·모니터링 및 재처리 기준서; 컴플라이언스 및 접근권한 검토서; 변경관리·릴리즈 계획서; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/1cf819585db94f2f5a76072cb4643a99c11da201</t>
         </is>
       </c>
     </row>
